--- a/data/PC/processed/crnp/PC_CRNP_daily.xlsx
+++ b/data/PC/processed/crnp/PC_CRNP_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N531"/>
+  <dimension ref="A1:O531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>Iref</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rain</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -545,6 +550,9 @@
       <c r="N2" t="n">
         <v>211.688</v>
       </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,6 +599,9 @@
       <c r="N3" t="n">
         <v>211.688</v>
       </c>
+      <c r="O3" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -637,6 +648,9 @@
       <c r="N4" t="n">
         <v>211.688</v>
       </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -683,6 +697,9 @@
       <c r="N5" t="n">
         <v>211.688</v>
       </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -729,6 +746,9 @@
       <c r="N6" t="n">
         <v>211.688</v>
       </c>
+      <c r="O6" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -775,6 +795,9 @@
       <c r="N7" t="n">
         <v>211.688</v>
       </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -821,6 +844,9 @@
       <c r="N8" t="n">
         <v>211.688</v>
       </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -867,6 +893,9 @@
       <c r="N9" t="n">
         <v>211.688</v>
       </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -913,6 +942,9 @@
       <c r="N10" t="n">
         <v>211.688</v>
       </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -959,6 +991,9 @@
       <c r="N11" t="n">
         <v>211.688</v>
       </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1005,6 +1040,9 @@
       <c r="N12" t="n">
         <v>211.688</v>
       </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1051,6 +1089,9 @@
       <c r="N13" t="n">
         <v>211.688</v>
       </c>
+      <c r="O13" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1097,6 +1138,9 @@
       <c r="N14" t="n">
         <v>211.688</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1143,6 +1187,9 @@
       <c r="N15" t="n">
         <v>211.688</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1189,6 +1236,9 @@
       <c r="N16" t="n">
         <v>211.688</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1235,6 +1285,9 @@
       <c r="N17" t="n">
         <v>211.688</v>
       </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1281,6 +1334,9 @@
       <c r="N18" t="n">
         <v>211.688</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1327,6 +1383,9 @@
       <c r="N19" t="n">
         <v>211.688</v>
       </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1373,6 +1432,9 @@
       <c r="N20" t="n">
         <v>211.688</v>
       </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1419,6 +1481,9 @@
       <c r="N21" t="n">
         <v>211.688</v>
       </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1465,6 +1530,9 @@
       <c r="N22" t="n">
         <v>211.688</v>
       </c>
+      <c r="O22" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1511,6 +1579,9 @@
       <c r="N23" t="n">
         <v>211.688</v>
       </c>
+      <c r="O23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1557,6 +1628,9 @@
       <c r="N24" t="n">
         <v>211.688</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1603,6 +1677,9 @@
       <c r="N25" t="n">
         <v>211.688</v>
       </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1649,6 +1726,9 @@
       <c r="N26" t="n">
         <v>211.688</v>
       </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1695,6 +1775,9 @@
       <c r="N27" t="n">
         <v>211.688</v>
       </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1741,6 +1824,9 @@
       <c r="N28" t="n">
         <v>211.688</v>
       </c>
+      <c r="O28" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1787,6 +1873,9 @@
       <c r="N29" t="n">
         <v>211.688</v>
       </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1833,6 +1922,9 @@
       <c r="N30" t="n">
         <v>211.688</v>
       </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1879,6 +1971,9 @@
       <c r="N31" t="n">
         <v>211.688</v>
       </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1925,6 +2020,9 @@
       <c r="N32" t="n">
         <v>211.688</v>
       </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1971,6 +2069,9 @@
       <c r="N33" t="n">
         <v>211.688</v>
       </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2017,6 +2118,9 @@
       <c r="N34" t="n">
         <v>211.688</v>
       </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2063,6 +2167,9 @@
       <c r="N35" t="n">
         <v>211.688</v>
       </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2109,6 +2216,9 @@
       <c r="N36" t="n">
         <v>211.688</v>
       </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2155,6 +2265,9 @@
       <c r="N37" t="n">
         <v>211.688</v>
       </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2201,6 +2314,9 @@
       <c r="N38" t="n">
         <v>211.688</v>
       </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2247,6 +2363,9 @@
       <c r="N39" t="n">
         <v>211.688</v>
       </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2293,6 +2412,9 @@
       <c r="N40" t="n">
         <v>211.688</v>
       </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2339,6 +2461,9 @@
       <c r="N41" t="n">
         <v>211.688</v>
       </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2385,6 +2510,9 @@
       <c r="N42" t="n">
         <v>211.688</v>
       </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2431,6 +2559,9 @@
       <c r="N43" t="n">
         <v>211.688</v>
       </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2477,6 +2608,9 @@
       <c r="N44" t="n">
         <v>211.688</v>
       </c>
+      <c r="O44" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2523,6 +2657,9 @@
       <c r="N45" t="n">
         <v>211.688</v>
       </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2569,6 +2706,9 @@
       <c r="N46" t="n">
         <v>211.688</v>
       </c>
+      <c r="O46" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2615,6 +2755,9 @@
       <c r="N47" t="n">
         <v>211.688</v>
       </c>
+      <c r="O47" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2661,6 +2804,9 @@
       <c r="N48" t="n">
         <v>211.688</v>
       </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2707,6 +2853,9 @@
       <c r="N49" t="n">
         <v>211.688</v>
       </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2753,6 +2902,9 @@
       <c r="N50" t="n">
         <v>211.688</v>
       </c>
+      <c r="O50" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2799,6 +2951,9 @@
       <c r="N51" t="n">
         <v>211.688</v>
       </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2845,6 +3000,9 @@
       <c r="N52" t="n">
         <v>211.688</v>
       </c>
+      <c r="O52" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2891,6 +3049,9 @@
       <c r="N53" t="n">
         <v>211.688</v>
       </c>
+      <c r="O53" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2937,6 +3098,9 @@
       <c r="N54" t="n">
         <v>211.688</v>
       </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2983,6 +3147,9 @@
       <c r="N55" t="n">
         <v>211.688</v>
       </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3029,6 +3196,9 @@
       <c r="N56" t="n">
         <v>211.688</v>
       </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3075,6 +3245,9 @@
       <c r="N57" t="n">
         <v>211.688</v>
       </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3121,6 +3294,9 @@
       <c r="N58" t="n">
         <v>211.688</v>
       </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3167,6 +3343,9 @@
       <c r="N59" t="n">
         <v>211.688</v>
       </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3213,6 +3392,9 @@
       <c r="N60" t="n">
         <v>211.688</v>
       </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3259,6 +3441,9 @@
       <c r="N61" t="n">
         <v>211.688</v>
       </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3305,6 +3490,9 @@
       <c r="N62" t="n">
         <v>211.688</v>
       </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3351,6 +3539,9 @@
       <c r="N63" t="n">
         <v>211.688</v>
       </c>
+      <c r="O63" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3397,6 +3588,9 @@
       <c r="N64" t="n">
         <v>211.688</v>
       </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3443,6 +3637,9 @@
       <c r="N65" t="n">
         <v>211.688</v>
       </c>
+      <c r="O65" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3489,6 +3686,9 @@
       <c r="N66" t="n">
         <v>211.688</v>
       </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3535,6 +3735,9 @@
       <c r="N67" t="n">
         <v>211.688</v>
       </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3581,6 +3784,9 @@
       <c r="N68" t="n">
         <v>211.688</v>
       </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3627,6 +3833,9 @@
       <c r="N69" t="n">
         <v>211.688</v>
       </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3673,6 +3882,9 @@
       <c r="N70" t="n">
         <v>211.688</v>
       </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3719,6 +3931,9 @@
       <c r="N71" t="n">
         <v>211.688</v>
       </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3765,6 +3980,9 @@
       <c r="N72" t="n">
         <v>211.688</v>
       </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3811,6 +4029,9 @@
       <c r="N73" t="n">
         <v>211.688</v>
       </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3857,6 +4078,9 @@
       <c r="N74" t="n">
         <v>211.688</v>
       </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3903,6 +4127,9 @@
       <c r="N75" t="n">
         <v>211.688</v>
       </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3949,6 +4176,9 @@
       <c r="N76" t="n">
         <v>211.688</v>
       </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3995,6 +4225,9 @@
       <c r="N77" t="n">
         <v>211.688</v>
       </c>
+      <c r="O77" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4041,6 +4274,9 @@
       <c r="N78" t="n">
         <v>211.688</v>
       </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4087,6 +4323,9 @@
       <c r="N79" t="n">
         <v>211.688</v>
       </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4133,6 +4372,9 @@
       <c r="N80" t="n">
         <v>211.688</v>
       </c>
+      <c r="O80" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4179,6 +4421,9 @@
       <c r="N81" t="n">
         <v>211.688</v>
       </c>
+      <c r="O81" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4225,6 +4470,9 @@
       <c r="N82" t="n">
         <v>211.688</v>
       </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4271,6 +4519,9 @@
       <c r="N83" t="n">
         <v>211.688</v>
       </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4317,6 +4568,9 @@
       <c r="N84" t="n">
         <v>211.688</v>
       </c>
+      <c r="O84" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4363,6 +4617,9 @@
       <c r="N85" t="n">
         <v>211.688</v>
       </c>
+      <c r="O85" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4409,6 +4666,9 @@
       <c r="N86" t="n">
         <v>211.688</v>
       </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4455,6 +4715,9 @@
       <c r="N87" t="n">
         <v>211.688</v>
       </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4501,6 +4764,9 @@
       <c r="N88" t="n">
         <v>211.688</v>
       </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4547,6 +4813,9 @@
       <c r="N89" t="n">
         <v>211.688</v>
       </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4593,6 +4862,9 @@
       <c r="N90" t="n">
         <v>211.688</v>
       </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4639,6 +4911,9 @@
       <c r="N91" t="n">
         <v>211.688</v>
       </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4685,6 +4960,9 @@
       <c r="N92" t="n">
         <v>211.688</v>
       </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4731,6 +5009,9 @@
       <c r="N93" t="n">
         <v>211.688</v>
       </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4777,6 +5058,9 @@
       <c r="N94" t="n">
         <v>211.688</v>
       </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4823,6 +5107,9 @@
       <c r="N95" t="n">
         <v>211.688</v>
       </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4869,6 +5156,9 @@
       <c r="N96" t="n">
         <v>211.688</v>
       </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4915,6 +5205,9 @@
       <c r="N97" t="n">
         <v>211.688</v>
       </c>
+      <c r="O97" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4961,6 +5254,9 @@
       <c r="N98" t="n">
         <v>211.688</v>
       </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5007,6 +5303,9 @@
       <c r="N99" t="n">
         <v>211.688</v>
       </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5053,6 +5352,9 @@
       <c r="N100" t="n">
         <v>211.688</v>
       </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5099,6 +5401,9 @@
       <c r="N101" t="n">
         <v>211.688</v>
       </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5145,6 +5450,9 @@
       <c r="N102" t="n">
         <v>211.688</v>
       </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5191,6 +5499,9 @@
       <c r="N103" t="n">
         <v>211.688</v>
       </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5237,6 +5548,9 @@
       <c r="N104" t="n">
         <v>211.688</v>
       </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5283,6 +5597,9 @@
       <c r="N105" t="n">
         <v>211.688</v>
       </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5329,6 +5646,9 @@
       <c r="N106" t="n">
         <v>211.688</v>
       </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5375,6 +5695,9 @@
       <c r="N107" t="n">
         <v>211.688</v>
       </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5421,6 +5744,9 @@
       <c r="N108" t="n">
         <v>211.688</v>
       </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5467,6 +5793,9 @@
       <c r="N109" t="n">
         <v>211.688</v>
       </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5513,6 +5842,9 @@
       <c r="N110" t="n">
         <v>211.688</v>
       </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5559,6 +5891,9 @@
       <c r="N111" t="n">
         <v>211.688</v>
       </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5605,6 +5940,9 @@
       <c r="N112" t="n">
         <v>211.688</v>
       </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5651,6 +5989,9 @@
       <c r="N113" t="n">
         <v>211.688</v>
       </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5697,6 +6038,9 @@
       <c r="N114" t="n">
         <v>211.688</v>
       </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5743,6 +6087,9 @@
       <c r="N115" t="n">
         <v>211.688</v>
       </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5789,6 +6136,9 @@
       <c r="N116" t="n">
         <v>211.688</v>
       </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5835,6 +6185,9 @@
       <c r="N117" t="n">
         <v>211.688</v>
       </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5881,6 +6234,9 @@
       <c r="N118" t="n">
         <v>211.688</v>
       </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5927,6 +6283,9 @@
       <c r="N119" t="n">
         <v>211.688</v>
       </c>
+      <c r="O119" t="n">
+        <v>23.5</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5973,6 +6332,9 @@
       <c r="N120" t="n">
         <v>211.688</v>
       </c>
+      <c r="O120" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6019,6 +6381,9 @@
       <c r="N121" t="n">
         <v>211.688</v>
       </c>
+      <c r="O121" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6065,6 +6430,9 @@
       <c r="N122" t="n">
         <v>211.688</v>
       </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6111,6 +6479,9 @@
       <c r="N123" t="n">
         <v>211.688</v>
       </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6157,6 +6528,9 @@
       <c r="N124" t="n">
         <v>211.688</v>
       </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6203,6 +6577,9 @@
       <c r="N125" t="n">
         <v>211.688</v>
       </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6249,6 +6626,9 @@
       <c r="N126" t="n">
         <v>211.688</v>
       </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6295,6 +6675,9 @@
       <c r="N127" t="n">
         <v>211.688</v>
       </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6341,6 +6724,9 @@
       <c r="N128" t="n">
         <v>211.688</v>
       </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6387,6 +6773,9 @@
       <c r="N129" t="n">
         <v>211.688</v>
       </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6433,6 +6822,9 @@
       <c r="N130" t="n">
         <v>211.688</v>
       </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6479,6 +6871,9 @@
       <c r="N131" t="n">
         <v>211.688</v>
       </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6525,6 +6920,9 @@
       <c r="N132" t="n">
         <v>211.688</v>
       </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6571,6 +6969,9 @@
       <c r="N133" t="n">
         <v>211.688</v>
       </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6617,6 +7018,9 @@
       <c r="N134" t="n">
         <v>211.688</v>
       </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6663,6 +7067,9 @@
       <c r="N135" t="n">
         <v>211.688</v>
       </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6709,6 +7116,9 @@
       <c r="N136" t="n">
         <v>211.688</v>
       </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6755,6 +7165,9 @@
       <c r="N137" t="n">
         <v>211.688</v>
       </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6801,6 +7214,9 @@
       <c r="N138" t="n">
         <v>211.688</v>
       </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6847,6 +7263,9 @@
       <c r="N139" t="n">
         <v>211.688</v>
       </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6893,6 +7312,9 @@
       <c r="N140" t="n">
         <v>211.688</v>
       </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6939,6 +7361,9 @@
       <c r="N141" t="n">
         <v>211.688</v>
       </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6985,6 +7410,9 @@
       <c r="N142" t="n">
         <v>211.688</v>
       </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7031,6 +7459,9 @@
       <c r="N143" t="n">
         <v>211.688</v>
       </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7077,6 +7508,9 @@
       <c r="N144" t="n">
         <v>211.688</v>
       </c>
+      <c r="O144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7123,6 +7557,9 @@
       <c r="N145" t="n">
         <v>211.688</v>
       </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7169,6 +7606,9 @@
       <c r="N146" t="n">
         <v>211.688</v>
       </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7215,6 +7655,9 @@
       <c r="N147" t="n">
         <v>211.688</v>
       </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7261,6 +7704,9 @@
       <c r="N148" t="n">
         <v>211.688</v>
       </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7307,6 +7753,9 @@
       <c r="N149" t="n">
         <v>211.688</v>
       </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7353,6 +7802,9 @@
       <c r="N150" t="n">
         <v>211.688</v>
       </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7399,6 +7851,9 @@
       <c r="N151" t="n">
         <v>211.688</v>
       </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7445,6 +7900,9 @@
       <c r="N152" t="n">
         <v>211.688</v>
       </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7491,6 +7949,9 @@
       <c r="N153" t="n">
         <v>211.688</v>
       </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7537,6 +7998,9 @@
       <c r="N154" t="n">
         <v>211.688</v>
       </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7583,6 +8047,9 @@
       <c r="N155" t="n">
         <v>211.688</v>
       </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7629,6 +8096,9 @@
       <c r="N156" t="n">
         <v>211.688</v>
       </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7675,6 +8145,9 @@
       <c r="N157" t="n">
         <v>211.688</v>
       </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7721,6 +8194,9 @@
       <c r="N158" t="n">
         <v>211.688</v>
       </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7767,6 +8243,9 @@
       <c r="N159" t="n">
         <v>211.688</v>
       </c>
+      <c r="O159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7813,6 +8292,9 @@
       <c r="N160" t="n">
         <v>211.688</v>
       </c>
+      <c r="O160" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7859,6 +8341,9 @@
       <c r="N161" t="n">
         <v>211.688</v>
       </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7905,6 +8390,9 @@
       <c r="N162" t="n">
         <v>211.688</v>
       </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7951,6 +8439,9 @@
       <c r="N163" t="n">
         <v>211.688</v>
       </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7997,6 +8488,9 @@
       <c r="N164" t="n">
         <v>211.688</v>
       </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8043,6 +8537,9 @@
       <c r="N165" t="n">
         <v>211.688</v>
       </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8089,6 +8586,9 @@
       <c r="N166" t="n">
         <v>211.688</v>
       </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8135,6 +8635,9 @@
       <c r="N167" t="n">
         <v>211.688</v>
       </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8181,6 +8684,9 @@
       <c r="N168" t="n">
         <v>211.688</v>
       </c>
+      <c r="O168" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8227,6 +8733,9 @@
       <c r="N169" t="n">
         <v>211.688</v>
       </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8273,6 +8782,9 @@
       <c r="N170" t="n">
         <v>211.688</v>
       </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8319,6 +8831,9 @@
       <c r="N171" t="n">
         <v>211.688</v>
       </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8365,6 +8880,9 @@
       <c r="N172" t="n">
         <v>211.688</v>
       </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8411,6 +8929,9 @@
       <c r="N173" t="n">
         <v>211.688</v>
       </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8457,6 +8978,9 @@
       <c r="N174" t="n">
         <v>211.688</v>
       </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8503,6 +9027,9 @@
       <c r="N175" t="n">
         <v>211.688</v>
       </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8549,6 +9076,9 @@
       <c r="N176" t="n">
         <v>211.688</v>
       </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8595,6 +9125,9 @@
       <c r="N177" t="n">
         <v>211.688</v>
       </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8641,6 +9174,9 @@
       <c r="N178" t="n">
         <v>211.688</v>
       </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8687,6 +9223,9 @@
       <c r="N179" t="n">
         <v>211.688</v>
       </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8733,6 +9272,9 @@
       <c r="N180" t="n">
         <v>211.688</v>
       </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8778,6 +9320,9 @@
       </c>
       <c r="N181" t="n">
         <v>211.688</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -8821,6 +9366,9 @@
       <c r="N182" t="n">
         <v>211.688</v>
       </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8863,6 +9411,9 @@
       <c r="N183" t="n">
         <v>211.688</v>
       </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8905,6 +9456,9 @@
       <c r="N184" t="n">
         <v>211.688</v>
       </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8947,6 +9501,9 @@
       <c r="N185" t="n">
         <v>211.688</v>
       </c>
+      <c r="O185" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8989,6 +9546,9 @@
       <c r="N186" t="n">
         <v>211.688</v>
       </c>
+      <c r="O186" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9031,6 +9591,9 @@
       <c r="N187" t="n">
         <v>211.688</v>
       </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9073,6 +9636,9 @@
       <c r="N188" t="n">
         <v>211.688</v>
       </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9115,6 +9681,9 @@
       <c r="N189" t="n">
         <v>211.688</v>
       </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9157,6 +9726,9 @@
       <c r="N190" t="n">
         <v>211.688</v>
       </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9199,6 +9771,9 @@
       <c r="N191" t="n">
         <v>211.688</v>
       </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9241,6 +9816,9 @@
       <c r="N192" t="n">
         <v>211.688</v>
       </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9283,6 +9861,9 @@
       <c r="N193" t="n">
         <v>211.688</v>
       </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9325,6 +9906,9 @@
       <c r="N194" t="n">
         <v>211.688</v>
       </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9367,6 +9951,9 @@
       <c r="N195" t="n">
         <v>211.688</v>
       </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9409,6 +9996,9 @@
       <c r="N196" t="n">
         <v>211.688</v>
       </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9451,6 +10041,9 @@
       <c r="N197" t="n">
         <v>211.688</v>
       </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9493,6 +10086,9 @@
       <c r="N198" t="n">
         <v>211.688</v>
       </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9535,6 +10131,9 @@
       <c r="N199" t="n">
         <v>211.688</v>
       </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9577,6 +10176,9 @@
       <c r="N200" t="n">
         <v>211.688</v>
       </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9619,6 +10221,9 @@
       <c r="N201" t="n">
         <v>211.688</v>
       </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9661,6 +10266,9 @@
       <c r="N202" t="n">
         <v>211.688</v>
       </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9703,6 +10311,9 @@
       <c r="N203" t="n">
         <v>211.688</v>
       </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9745,6 +10356,9 @@
       <c r="N204" t="n">
         <v>211.688</v>
       </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9787,6 +10401,9 @@
       <c r="N205" t="n">
         <v>211.688</v>
       </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9829,6 +10446,9 @@
       <c r="N206" t="n">
         <v>211.688</v>
       </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9871,6 +10491,9 @@
       <c r="N207" t="n">
         <v>211.688</v>
       </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9913,6 +10536,9 @@
       <c r="N208" t="n">
         <v>211.688</v>
       </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9955,6 +10581,9 @@
       <c r="N209" t="n">
         <v>211.688</v>
       </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9997,6 +10626,9 @@
       <c r="N210" t="n">
         <v>211.688</v>
       </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10039,6 +10671,9 @@
       <c r="N211" t="n">
         <v>211.688</v>
       </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10081,6 +10716,9 @@
       <c r="N212" t="n">
         <v>211.688</v>
       </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10123,6 +10761,9 @@
       <c r="N213" t="n">
         <v>211.688</v>
       </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10169,6 +10810,9 @@
       <c r="N214" t="n">
         <v>211.688</v>
       </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10214,6 +10858,9 @@
       </c>
       <c r="N215" t="n">
         <v>211.688</v>
+      </c>
+      <c r="O215" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -10257,6 +10904,9 @@
       <c r="N216" t="n">
         <v>211.688</v>
       </c>
+      <c r="O216" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10299,6 +10949,9 @@
       <c r="N217" t="n">
         <v>211.688</v>
       </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10341,6 +10994,9 @@
       <c r="N218" t="n">
         <v>211.688</v>
       </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10383,6 +11039,9 @@
       <c r="N219" t="n">
         <v>211.688</v>
       </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10425,6 +11084,9 @@
       <c r="N220" t="n">
         <v>211.688</v>
       </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10467,6 +11129,9 @@
       <c r="N221" t="n">
         <v>211.688</v>
       </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10513,6 +11178,9 @@
       <c r="N222" t="n">
         <v>211.688</v>
       </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10559,6 +11227,9 @@
       <c r="N223" t="n">
         <v>211.688</v>
       </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10605,6 +11276,9 @@
       <c r="N224" t="n">
         <v>211.688</v>
       </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10651,6 +11325,9 @@
       <c r="N225" t="n">
         <v>211.688</v>
       </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10697,6 +11374,9 @@
       <c r="N226" t="n">
         <v>211.688</v>
       </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10743,6 +11423,9 @@
       <c r="N227" t="n">
         <v>211.688</v>
       </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10789,6 +11472,9 @@
       <c r="N228" t="n">
         <v>211.688</v>
       </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10835,6 +11521,9 @@
       <c r="N229" t="n">
         <v>211.688</v>
       </c>
+      <c r="O229" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10881,6 +11570,9 @@
       <c r="N230" t="n">
         <v>211.688</v>
       </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10927,6 +11619,9 @@
       <c r="N231" t="n">
         <v>211.688</v>
       </c>
+      <c r="O231" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10973,6 +11668,9 @@
       <c r="N232" t="n">
         <v>211.688</v>
       </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11019,6 +11717,9 @@
       <c r="N233" t="n">
         <v>211.688</v>
       </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11065,6 +11766,9 @@
       <c r="N234" t="n">
         <v>211.688</v>
       </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11111,6 +11815,9 @@
       <c r="N235" t="n">
         <v>211.688</v>
       </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11157,6 +11864,9 @@
       <c r="N236" t="n">
         <v>211.688</v>
       </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11203,6 +11913,9 @@
       <c r="N237" t="n">
         <v>211.688</v>
       </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11249,6 +11962,9 @@
       <c r="N238" t="n">
         <v>211.688</v>
       </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11295,6 +12011,9 @@
       <c r="N239" t="n">
         <v>211.688</v>
       </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11341,6 +12060,9 @@
       <c r="N240" t="n">
         <v>211.688</v>
       </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11387,6 +12109,9 @@
       <c r="N241" t="n">
         <v>211.688</v>
       </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11433,6 +12158,9 @@
       <c r="N242" t="n">
         <v>211.688</v>
       </c>
+      <c r="O242" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11479,6 +12207,9 @@
       <c r="N243" t="n">
         <v>211.688</v>
       </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11525,6 +12256,9 @@
       <c r="N244" t="n">
         <v>211.688</v>
       </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11571,6 +12305,9 @@
       <c r="N245" t="n">
         <v>211.688</v>
       </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11617,6 +12354,9 @@
       <c r="N246" t="n">
         <v>211.688</v>
       </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11663,6 +12403,9 @@
       <c r="N247" t="n">
         <v>211.688</v>
       </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11709,6 +12452,9 @@
       <c r="N248" t="n">
         <v>211.688</v>
       </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11755,6 +12501,9 @@
       <c r="N249" t="n">
         <v>211.688</v>
       </c>
+      <c r="O249" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11801,6 +12550,9 @@
       <c r="N250" t="n">
         <v>211.688</v>
       </c>
+      <c r="O250" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11847,6 +12599,9 @@
       <c r="N251" t="n">
         <v>211.688</v>
       </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11893,6 +12648,9 @@
       <c r="N252" t="n">
         <v>211.688</v>
       </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11939,6 +12697,9 @@
       <c r="N253" t="n">
         <v>211.688</v>
       </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11985,6 +12746,9 @@
       <c r="N254" t="n">
         <v>211.688</v>
       </c>
+      <c r="O254" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12031,6 +12795,9 @@
       <c r="N255" t="n">
         <v>211.688</v>
       </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12077,6 +12844,9 @@
       <c r="N256" t="n">
         <v>211.688</v>
       </c>
+      <c r="O256" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12123,6 +12893,9 @@
       <c r="N257" t="n">
         <v>211.688</v>
       </c>
+      <c r="O257" t="n">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12169,6 +12942,9 @@
       <c r="N258" t="n">
         <v>211.688</v>
       </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12215,6 +12991,9 @@
       <c r="N259" t="n">
         <v>211.688</v>
       </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12261,6 +13040,9 @@
       <c r="N260" t="n">
         <v>211.688</v>
       </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12307,6 +13089,9 @@
       <c r="N261" t="n">
         <v>211.688</v>
       </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12353,6 +13138,9 @@
       <c r="N262" t="n">
         <v>211.688</v>
       </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12399,6 +13187,9 @@
       <c r="N263" t="n">
         <v>211.688</v>
       </c>
+      <c r="O263" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12445,6 +13236,9 @@
       <c r="N264" t="n">
         <v>211.688</v>
       </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12491,6 +13285,9 @@
       <c r="N265" t="n">
         <v>211.688</v>
       </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12537,6 +13334,9 @@
       <c r="N266" t="n">
         <v>211.688</v>
       </c>
+      <c r="O266" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12583,6 +13383,9 @@
       <c r="N267" t="n">
         <v>211.688</v>
       </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12629,6 +13432,9 @@
       <c r="N268" t="n">
         <v>211.688</v>
       </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12675,6 +13481,9 @@
       <c r="N269" t="n">
         <v>211.688</v>
       </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12721,6 +13530,9 @@
       <c r="N270" t="n">
         <v>211.688</v>
       </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12767,6 +13579,9 @@
       <c r="N271" t="n">
         <v>211.688</v>
       </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12813,6 +13628,9 @@
       <c r="N272" t="n">
         <v>211.688</v>
       </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -12859,6 +13677,9 @@
       <c r="N273" t="n">
         <v>211.688</v>
       </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12905,6 +13726,9 @@
       <c r="N274" t="n">
         <v>211.688</v>
       </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12951,6 +13775,9 @@
       <c r="N275" t="n">
         <v>211.688</v>
       </c>
+      <c r="O275" t="n">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -12997,6 +13824,9 @@
       <c r="N276" t="n">
         <v>211.688</v>
       </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13043,6 +13873,9 @@
       <c r="N277" t="n">
         <v>211.688</v>
       </c>
+      <c r="O277" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13089,6 +13922,9 @@
       <c r="N278" t="n">
         <v>211.688</v>
       </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -13135,6 +13971,9 @@
       <c r="N279" t="n">
         <v>211.688</v>
       </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -13181,6 +14020,9 @@
       <c r="N280" t="n">
         <v>211.688</v>
       </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -13227,6 +14069,9 @@
       <c r="N281" t="n">
         <v>211.688</v>
       </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13273,6 +14118,9 @@
       <c r="N282" t="n">
         <v>211.688</v>
       </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13319,6 +14167,9 @@
       <c r="N283" t="n">
         <v>211.688</v>
       </c>
+      <c r="O283" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13365,6 +14216,9 @@
       <c r="N284" t="n">
         <v>211.688</v>
       </c>
+      <c r="O284" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13411,6 +14265,9 @@
       <c r="N285" t="n">
         <v>211.688</v>
       </c>
+      <c r="O285" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13457,6 +14314,9 @@
       <c r="N286" t="n">
         <v>211.688</v>
       </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13503,6 +14363,9 @@
       <c r="N287" t="n">
         <v>211.688</v>
       </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13549,6 +14412,9 @@
       <c r="N288" t="n">
         <v>211.688</v>
       </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13595,6 +14461,9 @@
       <c r="N289" t="n">
         <v>211.688</v>
       </c>
+      <c r="O289" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13641,6 +14510,9 @@
       <c r="N290" t="n">
         <v>211.688</v>
       </c>
+      <c r="O290" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13687,6 +14559,9 @@
       <c r="N291" t="n">
         <v>211.688</v>
       </c>
+      <c r="O291" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13733,6 +14608,9 @@
       <c r="N292" t="n">
         <v>211.688</v>
       </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13779,6 +14657,9 @@
       <c r="N293" t="n">
         <v>211.688</v>
       </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13825,6 +14706,9 @@
       <c r="N294" t="n">
         <v>211.688</v>
       </c>
+      <c r="O294" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13871,6 +14755,9 @@
       <c r="N295" t="n">
         <v>211.688</v>
       </c>
+      <c r="O295" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13917,6 +14804,9 @@
       <c r="N296" t="n">
         <v>211.688</v>
       </c>
+      <c r="O296" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13963,6 +14853,9 @@
       <c r="N297" t="n">
         <v>211.688</v>
       </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14009,6 +14902,9 @@
       <c r="N298" t="n">
         <v>211.688</v>
       </c>
+      <c r="O298" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14055,6 +14951,9 @@
       <c r="N299" t="n">
         <v>211.688</v>
       </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14101,6 +15000,9 @@
       <c r="N300" t="n">
         <v>211.688</v>
       </c>
+      <c r="O300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14147,6 +15049,9 @@
       <c r="N301" t="n">
         <v>211.688</v>
       </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14193,6 +15098,9 @@
       <c r="N302" t="n">
         <v>211.688</v>
       </c>
+      <c r="O302" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14239,6 +15147,9 @@
       <c r="N303" t="n">
         <v>211.688</v>
       </c>
+      <c r="O303" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14285,6 +15196,9 @@
       <c r="N304" t="n">
         <v>211.688</v>
       </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14331,6 +15245,9 @@
       <c r="N305" t="n">
         <v>211.688</v>
       </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14377,6 +15294,9 @@
       <c r="N306" t="n">
         <v>211.688</v>
       </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14423,6 +15343,9 @@
       <c r="N307" t="n">
         <v>211.688</v>
       </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14469,6 +15392,9 @@
       <c r="N308" t="n">
         <v>211.688</v>
       </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14515,6 +15441,9 @@
       <c r="N309" t="n">
         <v>211.688</v>
       </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14561,6 +15490,9 @@
       <c r="N310" t="n">
         <v>211.688</v>
       </c>
+      <c r="O310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14607,6 +15539,9 @@
       <c r="N311" t="n">
         <v>211.688</v>
       </c>
+      <c r="O311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14653,6 +15588,9 @@
       <c r="N312" t="n">
         <v>211.688</v>
       </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14699,6 +15637,9 @@
       <c r="N313" t="n">
         <v>211.688</v>
       </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14745,6 +15686,9 @@
       <c r="N314" t="n">
         <v>211.688</v>
       </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14791,6 +15735,9 @@
       <c r="N315" t="n">
         <v>211.688</v>
       </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14837,6 +15784,9 @@
       <c r="N316" t="n">
         <v>211.688</v>
       </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14883,6 +15833,9 @@
       <c r="N317" t="n">
         <v>211.688</v>
       </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14929,6 +15882,9 @@
       <c r="N318" t="n">
         <v>211.688</v>
       </c>
+      <c r="O318" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14975,6 +15931,9 @@
       <c r="N319" t="n">
         <v>211.688</v>
       </c>
+      <c r="O319" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15021,6 +15980,9 @@
       <c r="N320" t="n">
         <v>211.688</v>
       </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15067,6 +16029,9 @@
       <c r="N321" t="n">
         <v>211.688</v>
       </c>
+      <c r="O321" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -15113,6 +16078,9 @@
       <c r="N322" t="n">
         <v>211.688</v>
       </c>
+      <c r="O322" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -15159,6 +16127,9 @@
       <c r="N323" t="n">
         <v>211.688</v>
       </c>
+      <c r="O323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15205,6 +16176,9 @@
       <c r="N324" t="n">
         <v>211.688</v>
       </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15251,6 +16225,9 @@
       <c r="N325" t="n">
         <v>211.688</v>
       </c>
+      <c r="O325" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15297,6 +16274,9 @@
       <c r="N326" t="n">
         <v>211.688</v>
       </c>
+      <c r="O326" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15343,6 +16323,9 @@
       <c r="N327" t="n">
         <v>211.688</v>
       </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15389,6 +16372,9 @@
       <c r="N328" t="n">
         <v>211.688</v>
       </c>
+      <c r="O328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15435,6 +16421,9 @@
       <c r="N329" t="n">
         <v>211.688</v>
       </c>
+      <c r="O329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15481,6 +16470,9 @@
       <c r="N330" t="n">
         <v>211.688</v>
       </c>
+      <c r="O330" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15527,6 +16519,9 @@
       <c r="N331" t="n">
         <v>211.688</v>
       </c>
+      <c r="O331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15573,6 +16568,9 @@
       <c r="N332" t="n">
         <v>211.688</v>
       </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15619,6 +16617,9 @@
       <c r="N333" t="n">
         <v>211.688</v>
       </c>
+      <c r="O333" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15665,6 +16666,9 @@
       <c r="N334" t="n">
         <v>211.688</v>
       </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15711,6 +16715,9 @@
       <c r="N335" t="n">
         <v>211.688</v>
       </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15757,6 +16764,9 @@
       <c r="N336" t="n">
         <v>211.688</v>
       </c>
+      <c r="O336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15803,6 +16813,9 @@
       <c r="N337" t="n">
         <v>211.688</v>
       </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15849,6 +16862,9 @@
       <c r="N338" t="n">
         <v>211.688</v>
       </c>
+      <c r="O338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15895,6 +16911,9 @@
       <c r="N339" t="n">
         <v>211.688</v>
       </c>
+      <c r="O339" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15941,6 +16960,9 @@
       <c r="N340" t="n">
         <v>211.688</v>
       </c>
+      <c r="O340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -15987,6 +17009,9 @@
       <c r="N341" t="n">
         <v>211.688</v>
       </c>
+      <c r="O341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16033,6 +17058,9 @@
       <c r="N342" t="n">
         <v>211.688</v>
       </c>
+      <c r="O342" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16079,6 +17107,9 @@
       <c r="N343" t="n">
         <v>211.688</v>
       </c>
+      <c r="O343" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -16125,6 +17156,9 @@
       <c r="N344" t="n">
         <v>211.688</v>
       </c>
+      <c r="O344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -16171,6 +17205,9 @@
       <c r="N345" t="n">
         <v>211.688</v>
       </c>
+      <c r="O345" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16217,6 +17254,9 @@
       <c r="N346" t="n">
         <v>211.688</v>
       </c>
+      <c r="O346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -16263,6 +17303,9 @@
       <c r="N347" t="n">
         <v>211.688</v>
       </c>
+      <c r="O347" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -16309,6 +17352,9 @@
       <c r="N348" t="n">
         <v>211.688</v>
       </c>
+      <c r="O348" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16355,6 +17401,9 @@
       <c r="N349" t="n">
         <v>211.688</v>
       </c>
+      <c r="O349" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16401,6 +17450,9 @@
       <c r="N350" t="n">
         <v>211.688</v>
       </c>
+      <c r="O350" t="n">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16447,6 +17499,9 @@
       <c r="N351" t="n">
         <v>211.688</v>
       </c>
+      <c r="O351" t="n">
+        <v>26.5</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16493,6 +17548,9 @@
       <c r="N352" t="n">
         <v>211.688</v>
       </c>
+      <c r="O352" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16539,6 +17597,9 @@
       <c r="N353" t="n">
         <v>211.688</v>
       </c>
+      <c r="O353" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16585,6 +17646,9 @@
       <c r="N354" t="n">
         <v>211.688</v>
       </c>
+      <c r="O354" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16631,6 +17695,9 @@
       <c r="N355" t="n">
         <v>211.688</v>
       </c>
+      <c r="O355" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16677,6 +17744,9 @@
       <c r="N356" t="n">
         <v>211.688</v>
       </c>
+      <c r="O356" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16723,6 +17793,9 @@
       <c r="N357" t="n">
         <v>211.688</v>
       </c>
+      <c r="O357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16769,6 +17842,9 @@
       <c r="N358" t="n">
         <v>211.688</v>
       </c>
+      <c r="O358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16815,6 +17891,9 @@
       <c r="N359" t="n">
         <v>211.688</v>
       </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -16861,6 +17940,9 @@
       <c r="N360" t="n">
         <v>211.688</v>
       </c>
+      <c r="O360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -16907,6 +17989,9 @@
       <c r="N361" t="n">
         <v>211.688</v>
       </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -16953,6 +18038,9 @@
       <c r="N362" t="n">
         <v>211.688</v>
       </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16999,6 +18087,9 @@
       <c r="N363" t="n">
         <v>211.688</v>
       </c>
+      <c r="O363" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -17045,6 +18136,9 @@
       <c r="N364" t="n">
         <v>211.688</v>
       </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -17091,6 +18185,9 @@
       <c r="N365" t="n">
         <v>211.688</v>
       </c>
+      <c r="O365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -17137,6 +18234,9 @@
       <c r="N366" t="n">
         <v>211.688</v>
       </c>
+      <c r="O366" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -17183,6 +18283,9 @@
       <c r="N367" t="n">
         <v>211.688</v>
       </c>
+      <c r="O367" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -17229,6 +18332,9 @@
       <c r="N368" t="n">
         <v>211.688</v>
       </c>
+      <c r="O368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -17275,6 +18381,9 @@
       <c r="N369" t="n">
         <v>211.688</v>
       </c>
+      <c r="O369" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -17321,6 +18430,9 @@
       <c r="N370" t="n">
         <v>211.688</v>
       </c>
+      <c r="O370" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -17367,6 +18479,9 @@
       <c r="N371" t="n">
         <v>211.688</v>
       </c>
+      <c r="O371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -17413,6 +18528,9 @@
       <c r="N372" t="n">
         <v>211.688</v>
       </c>
+      <c r="O372" t="n">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -17459,6 +18577,9 @@
       <c r="N373" t="n">
         <v>211.688</v>
       </c>
+      <c r="O373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -17505,6 +18626,9 @@
       <c r="N374" t="n">
         <v>211.688</v>
       </c>
+      <c r="O374" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17551,6 +18675,9 @@
       <c r="N375" t="n">
         <v>211.688</v>
       </c>
+      <c r="O375" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -17597,6 +18724,9 @@
       <c r="N376" t="n">
         <v>211.688</v>
       </c>
+      <c r="O376" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -17643,6 +18773,9 @@
       <c r="N377" t="n">
         <v>211.688</v>
       </c>
+      <c r="O377" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -17689,6 +18822,9 @@
       <c r="N378" t="n">
         <v>211.688</v>
       </c>
+      <c r="O378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17735,6 +18871,9 @@
       <c r="N379" t="n">
         <v>211.688</v>
       </c>
+      <c r="O379" t="n">
+        <v>26.5</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -17781,6 +18920,9 @@
       <c r="N380" t="n">
         <v>211.688</v>
       </c>
+      <c r="O380" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -17827,6 +18969,9 @@
       <c r="N381" t="n">
         <v>211.688</v>
       </c>
+      <c r="O381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -17873,6 +19018,9 @@
       <c r="N382" t="n">
         <v>211.688</v>
       </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -17919,6 +19067,9 @@
       <c r="N383" t="n">
         <v>211.688</v>
       </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -17965,6 +19116,9 @@
       <c r="N384" t="n">
         <v>211.688</v>
       </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -18011,6 +19165,9 @@
       <c r="N385" t="n">
         <v>211.688</v>
       </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -18057,6 +19214,9 @@
       <c r="N386" t="n">
         <v>211.688</v>
       </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -18103,6 +19263,9 @@
       <c r="N387" t="n">
         <v>211.688</v>
       </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -18149,6 +19312,9 @@
       <c r="N388" t="n">
         <v>211.688</v>
       </c>
+      <c r="O388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -18195,6 +19361,9 @@
       <c r="N389" t="n">
         <v>211.688</v>
       </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -18241,6 +19410,9 @@
       <c r="N390" t="n">
         <v>211.688</v>
       </c>
+      <c r="O390" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -18287,6 +19459,9 @@
       <c r="N391" t="n">
         <v>211.688</v>
       </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -18333,6 +19508,9 @@
       <c r="N392" t="n">
         <v>211.688</v>
       </c>
+      <c r="O392" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -18379,6 +19557,9 @@
       <c r="N393" t="n">
         <v>211.688</v>
       </c>
+      <c r="O393" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -18425,6 +19606,9 @@
       <c r="N394" t="n">
         <v>211.688</v>
       </c>
+      <c r="O394" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -18471,6 +19655,9 @@
       <c r="N395" t="n">
         <v>211.688</v>
       </c>
+      <c r="O395" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -18517,6 +19704,9 @@
       <c r="N396" t="n">
         <v>211.688</v>
       </c>
+      <c r="O396" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -18563,6 +19753,9 @@
       <c r="N397" t="n">
         <v>211.688</v>
       </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -18609,6 +19802,9 @@
       <c r="N398" t="n">
         <v>211.688</v>
       </c>
+      <c r="O398" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -18655,6 +19851,9 @@
       <c r="N399" t="n">
         <v>211.688</v>
       </c>
+      <c r="O399" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18701,6 +19900,9 @@
       <c r="N400" t="n">
         <v>211.688</v>
       </c>
+      <c r="O400" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -18747,6 +19949,9 @@
       <c r="N401" t="n">
         <v>211.688</v>
       </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -18793,6 +19998,9 @@
       <c r="N402" t="n">
         <v>211.688</v>
       </c>
+      <c r="O402" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -18839,6 +20047,9 @@
       <c r="N403" t="n">
         <v>211.688</v>
       </c>
+      <c r="O403" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -18885,6 +20096,9 @@
       <c r="N404" t="n">
         <v>211.688</v>
       </c>
+      <c r="O404" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -18931,6 +20145,9 @@
       <c r="N405" t="n">
         <v>211.688</v>
       </c>
+      <c r="O405" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -18977,6 +20194,9 @@
       <c r="N406" t="n">
         <v>211.688</v>
       </c>
+      <c r="O406" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -19023,6 +20243,9 @@
       <c r="N407" t="n">
         <v>211.688</v>
       </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -19069,6 +20292,9 @@
       <c r="N408" t="n">
         <v>211.688</v>
       </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -19115,6 +20341,9 @@
       <c r="N409" t="n">
         <v>211.688</v>
       </c>
+      <c r="O409" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -19161,6 +20390,9 @@
       <c r="N410" t="n">
         <v>211.688</v>
       </c>
+      <c r="O410" t="n">
+        <v>42.5</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -19207,6 +20439,9 @@
       <c r="N411" t="n">
         <v>211.688</v>
       </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -19253,6 +20488,9 @@
       <c r="N412" t="n">
         <v>211.688</v>
       </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -19299,6 +20537,9 @@
       <c r="N413" t="n">
         <v>211.688</v>
       </c>
+      <c r="O413" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -19345,6 +20586,9 @@
       <c r="N414" t="n">
         <v>211.688</v>
       </c>
+      <c r="O414" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -19391,6 +20635,9 @@
       <c r="N415" t="n">
         <v>211.688</v>
       </c>
+      <c r="O415" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -19437,6 +20684,9 @@
       <c r="N416" t="n">
         <v>211.688</v>
       </c>
+      <c r="O416" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -19483,6 +20733,9 @@
       <c r="N417" t="n">
         <v>211.688</v>
       </c>
+      <c r="O417" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -19529,6 +20782,9 @@
       <c r="N418" t="n">
         <v>211.688</v>
       </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -19575,6 +20831,9 @@
       <c r="N419" t="n">
         <v>211.688</v>
       </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -19621,6 +20880,9 @@
       <c r="N420" t="n">
         <v>211.688</v>
       </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -19667,6 +20929,9 @@
       <c r="N421" t="n">
         <v>211.688</v>
       </c>
+      <c r="O421" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -19713,6 +20978,9 @@
       <c r="N422" t="n">
         <v>211.688</v>
       </c>
+      <c r="O422" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -19759,6 +21027,9 @@
       <c r="N423" t="n">
         <v>211.688</v>
       </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -19805,6 +21076,9 @@
       <c r="N424" t="n">
         <v>211.688</v>
       </c>
+      <c r="O424" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -19851,6 +21125,9 @@
       <c r="N425" t="n">
         <v>211.688</v>
       </c>
+      <c r="O425" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -19897,6 +21174,9 @@
       <c r="N426" t="n">
         <v>211.688</v>
       </c>
+      <c r="O426" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -19943,6 +21223,9 @@
       <c r="N427" t="n">
         <v>211.688</v>
       </c>
+      <c r="O427" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -19989,6 +21272,9 @@
       <c r="N428" t="n">
         <v>211.688</v>
       </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -20035,6 +21321,9 @@
       <c r="N429" t="n">
         <v>211.688</v>
       </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -20081,6 +21370,9 @@
       <c r="N430" t="n">
         <v>211.688</v>
       </c>
+      <c r="O430" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20127,6 +21419,9 @@
       <c r="N431" t="n">
         <v>211.688</v>
       </c>
+      <c r="O431" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -20173,6 +21468,9 @@
       <c r="N432" t="n">
         <v>211.688</v>
       </c>
+      <c r="O432" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -20219,6 +21517,9 @@
       <c r="N433" t="n">
         <v>211.688</v>
       </c>
+      <c r="O433" t="n">
+        <v>39.5</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -20265,6 +21566,9 @@
       <c r="N434" t="n">
         <v>211.688</v>
       </c>
+      <c r="O434" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -20311,6 +21615,9 @@
       <c r="N435" t="n">
         <v>211.688</v>
       </c>
+      <c r="O435" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -20357,6 +21664,9 @@
       <c r="N436" t="n">
         <v>211.688</v>
       </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -20403,6 +21713,9 @@
       <c r="N437" t="n">
         <v>211.688</v>
       </c>
+      <c r="O437" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -20449,6 +21762,9 @@
       <c r="N438" t="n">
         <v>211.688</v>
       </c>
+      <c r="O438" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -20495,6 +21811,9 @@
       <c r="N439" t="n">
         <v>211.688</v>
       </c>
+      <c r="O439" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -20541,6 +21860,9 @@
       <c r="N440" t="n">
         <v>211.688</v>
       </c>
+      <c r="O440" t="n">
+        <v>32.5</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -20587,6 +21909,9 @@
       <c r="N441" t="n">
         <v>211.688</v>
       </c>
+      <c r="O441" t="n">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -20633,6 +21958,9 @@
       <c r="N442" t="n">
         <v>211.688</v>
       </c>
+      <c r="O442" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -20679,6 +22007,9 @@
       <c r="N443" t="n">
         <v>211.688</v>
       </c>
+      <c r="O443" t="n">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -20725,6 +22056,9 @@
       <c r="N444" t="n">
         <v>211.688</v>
       </c>
+      <c r="O444" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -20771,6 +22105,9 @@
       <c r="N445" t="n">
         <v>211.688</v>
       </c>
+      <c r="O445" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -20817,6 +22154,9 @@
       <c r="N446" t="n">
         <v>211.688</v>
       </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -20863,6 +22203,9 @@
       <c r="N447" t="n">
         <v>211.688</v>
       </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -20909,6 +22252,9 @@
       <c r="N448" t="n">
         <v>211.688</v>
       </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -20955,6 +22301,9 @@
       <c r="N449" t="n">
         <v>211.688</v>
       </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -21001,6 +22350,9 @@
       <c r="N450" t="n">
         <v>211.688</v>
       </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -21047,6 +22399,9 @@
       <c r="N451" t="n">
         <v>211.688</v>
       </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -21093,6 +22448,9 @@
       <c r="N452" t="n">
         <v>211.688</v>
       </c>
+      <c r="O452" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -21139,6 +22497,9 @@
       <c r="N453" t="n">
         <v>211.688</v>
       </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -21185,6 +22546,9 @@
       <c r="N454" t="n">
         <v>211.688</v>
       </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -21231,6 +22595,9 @@
       <c r="N455" t="n">
         <v>211.688</v>
       </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -21277,6 +22644,9 @@
       <c r="N456" t="n">
         <v>211.688</v>
       </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -21323,6 +22693,9 @@
       <c r="N457" t="n">
         <v>211.688</v>
       </c>
+      <c r="O457" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -21369,6 +22742,9 @@
       <c r="N458" t="n">
         <v>211.688</v>
       </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -21415,6 +22791,9 @@
       <c r="N459" t="n">
         <v>211.688</v>
       </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -21461,6 +22840,9 @@
       <c r="N460" t="n">
         <v>211.688</v>
       </c>
+      <c r="O460" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -21507,6 +22889,9 @@
       <c r="N461" t="n">
         <v>211.688</v>
       </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -21553,6 +22938,9 @@
       <c r="N462" t="n">
         <v>211.688</v>
       </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -21599,6 +22987,9 @@
       <c r="N463" t="n">
         <v>211.688</v>
       </c>
+      <c r="O463" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -21645,6 +23036,9 @@
       <c r="N464" t="n">
         <v>211.688</v>
       </c>
+      <c r="O464" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -21691,6 +23085,9 @@
       <c r="N465" t="n">
         <v>211.688</v>
       </c>
+      <c r="O465" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -21737,6 +23134,9 @@
       <c r="N466" t="n">
         <v>211.688</v>
       </c>
+      <c r="O466" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -21783,6 +23183,9 @@
       <c r="N467" t="n">
         <v>211.688</v>
       </c>
+      <c r="O467" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -21829,6 +23232,9 @@
       <c r="N468" t="n">
         <v>211.688</v>
       </c>
+      <c r="O468" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -21875,6 +23281,9 @@
       <c r="N469" t="n">
         <v>211.688</v>
       </c>
+      <c r="O469" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -21921,6 +23330,9 @@
       <c r="N470" t="n">
         <v>211.688</v>
       </c>
+      <c r="O470" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -21967,6 +23379,9 @@
       <c r="N471" t="n">
         <v>211.688</v>
       </c>
+      <c r="O471" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -22013,6 +23428,9 @@
       <c r="N472" t="n">
         <v>211.688</v>
       </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -22059,6 +23477,9 @@
       <c r="N473" t="n">
         <v>211.688</v>
       </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -22105,6 +23526,9 @@
       <c r="N474" t="n">
         <v>211.688</v>
       </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -22151,6 +23575,9 @@
       <c r="N475" t="n">
         <v>211.688</v>
       </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -22197,6 +23624,9 @@
       <c r="N476" t="n">
         <v>211.688</v>
       </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -22243,6 +23673,9 @@
       <c r="N477" t="n">
         <v>211.688</v>
       </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -22289,6 +23722,9 @@
       <c r="N478" t="n">
         <v>211.688</v>
       </c>
+      <c r="O478" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -22335,6 +23771,9 @@
       <c r="N479" t="n">
         <v>211.688</v>
       </c>
+      <c r="O479" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -22381,6 +23820,9 @@
       <c r="N480" t="n">
         <v>211.688</v>
       </c>
+      <c r="O480" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -22427,6 +23869,9 @@
       <c r="N481" t="n">
         <v>211.688</v>
       </c>
+      <c r="O481" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -22473,6 +23918,9 @@
       <c r="N482" t="n">
         <v>211.688</v>
       </c>
+      <c r="O482" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -22519,6 +23967,9 @@
       <c r="N483" t="n">
         <v>211.688</v>
       </c>
+      <c r="O483" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -22565,6 +24016,9 @@
       <c r="N484" t="n">
         <v>211.688</v>
       </c>
+      <c r="O484" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -22611,6 +24065,9 @@
       <c r="N485" t="n">
         <v>211.688</v>
       </c>
+      <c r="O485" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -22657,6 +24114,9 @@
       <c r="N486" t="n">
         <v>211.688</v>
       </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -22703,6 +24163,9 @@
       <c r="N487" t="n">
         <v>211.688</v>
       </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -22749,6 +24212,9 @@
       <c r="N488" t="n">
         <v>211.688</v>
       </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -22795,6 +24261,9 @@
       <c r="N489" t="n">
         <v>211.688</v>
       </c>
+      <c r="O489" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -22841,6 +24310,9 @@
       <c r="N490" t="n">
         <v>211.688</v>
       </c>
+      <c r="O490" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -22887,6 +24359,9 @@
       <c r="N491" t="n">
         <v>211.688</v>
       </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -22933,6 +24408,9 @@
       <c r="N492" t="n">
         <v>211.688</v>
       </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -22979,6 +24457,9 @@
       <c r="N493" t="n">
         <v>211.688</v>
       </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -23025,6 +24506,9 @@
       <c r="N494" t="n">
         <v>211.688</v>
       </c>
+      <c r="O494" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -23071,6 +24555,9 @@
       <c r="N495" t="n">
         <v>211.688</v>
       </c>
+      <c r="O495" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -23117,6 +24604,9 @@
       <c r="N496" t="n">
         <v>211.688</v>
       </c>
+      <c r="O496" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -23163,6 +24653,9 @@
       <c r="N497" t="n">
         <v>211.688</v>
       </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -23209,6 +24702,9 @@
       <c r="N498" t="n">
         <v>211.688</v>
       </c>
+      <c r="O498" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -23255,6 +24751,9 @@
       <c r="N499" t="n">
         <v>211.688</v>
       </c>
+      <c r="O499" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -23301,6 +24800,9 @@
       <c r="N500" t="n">
         <v>211.688</v>
       </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -23347,6 +24849,9 @@
       <c r="N501" t="n">
         <v>211.688</v>
       </c>
+      <c r="O501" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -23393,6 +24898,9 @@
       <c r="N502" t="n">
         <v>211.688</v>
       </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -23439,6 +24947,9 @@
       <c r="N503" t="n">
         <v>211.688</v>
       </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -23485,6 +24996,9 @@
       <c r="N504" t="n">
         <v>211.688</v>
       </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -23531,6 +25045,9 @@
       <c r="N505" t="n">
         <v>211.688</v>
       </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -23577,6 +25094,9 @@
       <c r="N506" t="n">
         <v>211.688</v>
       </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -23623,6 +25143,9 @@
       <c r="N507" t="n">
         <v>211.688</v>
       </c>
+      <c r="O507" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -23669,6 +25192,9 @@
       <c r="N508" t="n">
         <v>211.688</v>
       </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -23715,6 +25241,9 @@
       <c r="N509" t="n">
         <v>211.688</v>
       </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -23761,6 +25290,9 @@
       <c r="N510" t="n">
         <v>211.688</v>
       </c>
+      <c r="O510" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -23807,6 +25339,9 @@
       <c r="N511" t="n">
         <v>211.688</v>
       </c>
+      <c r="O511" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -23853,6 +25388,9 @@
       <c r="N512" t="n">
         <v>211.688</v>
       </c>
+      <c r="O512" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -23899,6 +25437,9 @@
       <c r="N513" t="n">
         <v>211.688</v>
       </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -23945,6 +25486,9 @@
       <c r="N514" t="n">
         <v>211.688</v>
       </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -23991,6 +25535,9 @@
       <c r="N515" t="n">
         <v>211.688</v>
       </c>
+      <c r="O515" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -24037,6 +25584,9 @@
       <c r="N516" t="n">
         <v>211.688</v>
       </c>
+      <c r="O516" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -24083,6 +25633,9 @@
       <c r="N517" t="n">
         <v>211.688</v>
       </c>
+      <c r="O517" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -24129,6 +25682,9 @@
       <c r="N518" t="n">
         <v>211.688</v>
       </c>
+      <c r="O518" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -24175,6 +25731,9 @@
       <c r="N519" t="n">
         <v>211.688</v>
       </c>
+      <c r="O519" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -24221,6 +25780,9 @@
       <c r="N520" t="n">
         <v>211.688</v>
       </c>
+      <c r="O520" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -24267,6 +25829,9 @@
       <c r="N521" t="n">
         <v>211.688</v>
       </c>
+      <c r="O521" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -24313,6 +25878,9 @@
       <c r="N522" t="n">
         <v>211.688</v>
       </c>
+      <c r="O522" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -24359,6 +25927,9 @@
       <c r="N523" t="n">
         <v>211.688</v>
       </c>
+      <c r="O523" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -24405,6 +25976,9 @@
       <c r="N524" t="n">
         <v>211.688</v>
       </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -24451,6 +26025,9 @@
       <c r="N525" t="n">
         <v>211.688</v>
       </c>
+      <c r="O525" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -24497,6 +26074,9 @@
       <c r="N526" t="n">
         <v>211.688</v>
       </c>
+      <c r="O526" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -24543,6 +26123,9 @@
       <c r="N527" t="n">
         <v>211.688</v>
       </c>
+      <c r="O527" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -24589,6 +26172,9 @@
       <c r="N528" t="n">
         <v>211.688</v>
       </c>
+      <c r="O528" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -24635,6 +26221,9 @@
       <c r="N529" t="n">
         <v>211.688</v>
       </c>
+      <c r="O529" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -24681,6 +26270,9 @@
       <c r="N530" t="n">
         <v>211.688</v>
       </c>
+      <c r="O530" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -24726,6 +26318,9 @@
       </c>
       <c r="N531" t="n">
         <v>211.688</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
